--- a/data-manipulation-scripts/sheets-cleanup/sheets/CAMBIO COMPLETO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CAMBIO COMPLETO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -34,7 +34,7 @@
     <t>602883766150</t>
   </si>
   <si>
-    <t>CAMBIO COMPLETO IRON CG TITAN150 2004 A 2008 187976</t>
+    <t>CAMBIO COMPLETO IRON CG TITAN150 KS 2004 A 2008 187976</t>
   </si>
   <si>
     <t>602883766594</t>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>CAMBIO COMPLETO YBR125/ XTZ125 ATÉ 2007 188614</t>
+  </si>
+  <si>
+    <t>CAMBIO COMPLETO RIIE CG TITAN FAN125 2000 A 2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -131,7 +137,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -401,7 +407,9 @@
       <c r="C2" s="4">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>335.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -429,13 +437,15 @@
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="4">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>430.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -505,7 +515,9 @@
       <c r="C5" s="7">
         <v>1.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="5">
+        <v>310.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -539,7 +551,9 @@
       <c r="C6" s="7">
         <v>1.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="5">
+        <v>310.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -573,7 +587,9 @@
       <c r="C7" s="7">
         <v>1.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5">
+        <v>300.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -607,7 +623,9 @@
       <c r="C8" s="7">
         <v>1.0</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5">
+        <v>400.0</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -669,9 +687,15 @@
     </row>
     <row r="10">
       <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>310.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8"/>
@@ -680,7 +704,9 @@
       <c r="D11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="8"/>
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
